--- a/public/system/export/borrowlabs.xlsx
+++ b/public/system/export/borrowlabs.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>STT</t>
   </si>
@@ -51,16 +51,10 @@
     <t>TỔ CM</t>
   </si>
   <si>
-    <t>Quản Trị Viên</t>
-  </si>
-  <si>
     <t>Giáo Viên</t>
   </si>
   <si>
     <t>x</t>
-  </si>
-  <si>
-    <t>Thể dục - Quốc phòng-AN</t>
   </si>
   <si>
     <t>PBM
@@ -611,7 +605,7 @@
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1">
       <c r="A4" s="24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
@@ -640,20 +634,20 @@
         <v>7</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -663,7 +657,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -686,82 +680,58 @@
         <v>0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="G9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="H9" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="I9" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="J9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="16" t="s">
+      <c r="K9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="L9" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1">
       <c r="A10" s="6">
         <v>1</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0</v>
-      </c>
-      <c r="I10" s="21">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1">
       <c r="A11" s="6">
